--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\code\OpenCSTL\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E8570A-263B-4DC6-920D-C2A9CFB3F7B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518410F7-6DC0-4908-B8FF-B6284058C9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26580" yWindow="2190" windowWidth="23820" windowHeight="12105" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="4035" yWindow="3870" windowWidth="28800" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +62,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>header</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Container Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -135,14 +142,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>float_key</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float_value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>type*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,24 +176,60 @@
   <si>
     <t>typename</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opencstl_unordered_map</t>
+  </si>
+  <si>
+    <t>opencstl_unordered_set</t>
+  </si>
+  <si>
+    <t>OPENCSTL_UNORDERED_SET</t>
+  </si>
+  <si>
+    <t>OPENCSTL_UNORDERED_MAP</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>header(void*)</t>
+  </si>
+  <si>
+    <t>compare func</t>
+  </si>
+  <si>
+    <t>hash func</t>
+  </si>
+  <si>
+    <t>bloom filter</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>type_value</t>
+  </si>
+  <si>
+    <t>type_key</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -203,13 +238,29 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,6 +288,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,7 +338,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -294,10 +351,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -317,6 +371,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -336,9 +402,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -376,7 +442,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -482,7 +548,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -624,7 +690,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -632,16 +698,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE06D03-E65E-4121-BF89-D913E6F20D39}">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.75" customWidth="1"/>
-    <col min="3" max="3" width="26.125" customWidth="1"/>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="6" max="6" width="10.125" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -654,336 +724,410 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C2" s="11" t="s">
+    <row r="2" spans="1:15">
+      <c r="C2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="C3" s="5">
+        <v>-10</v>
+      </c>
+      <c r="D3" s="5">
+        <v>-9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>-8</v>
+      </c>
+      <c r="F3" s="6">
+        <v>-7</v>
+      </c>
+      <c r="G3" s="6">
+        <v>-6</v>
+      </c>
+      <c r="H3" s="6">
+        <v>-5</v>
+      </c>
+      <c r="I3" s="6">
+        <v>-4</v>
+      </c>
+      <c r="J3" s="6">
+        <v>-3</v>
+      </c>
+      <c r="K3" s="6">
+        <v>-2</v>
+      </c>
+      <c r="L3" s="6">
+        <v>-1</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <v>1</v>
+      </c>
+      <c r="O3" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C3" s="6">
-        <v>-8</v>
-      </c>
-      <c r="D3" s="7">
-        <v>-7</v>
-      </c>
-      <c r="E3" s="7">
-        <v>-6</v>
-      </c>
-      <c r="F3" s="7">
-        <v>-5</v>
-      </c>
-      <c r="G3" s="7">
-        <v>-4</v>
-      </c>
-      <c r="H3" s="7">
-        <v>-3</v>
-      </c>
-      <c r="I3" s="7">
-        <v>-2</v>
-      </c>
-      <c r="J3" s="7">
-        <v>-1</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>10</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="9"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="8"/>
+      <c r="O4" s="4"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="10" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>3</v>
-      </c>
+      <c r="I6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="J14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="M14" s="11" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518410F7-6DC0-4908-B8FF-B6284058C9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520E84C9-2400-4FC6-B6F2-D23AA903792C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4035" yWindow="3870" windowWidth="28800" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="1185" yWindow="5745" windowWidth="32055" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="51">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -193,9 +193,6 @@
     <t>base</t>
   </si>
   <si>
-    <t>header(void*)</t>
-  </si>
-  <si>
     <t>compare func</t>
   </si>
   <si>
@@ -212,13 +209,28 @@
   </si>
   <si>
     <t>type_key</t>
+  </si>
+  <si>
+    <t>is_float_key</t>
+  </si>
+  <si>
+    <t>is_float_value</t>
+  </si>
+  <si>
+    <t>arena</t>
+  </si>
+  <si>
+    <t>freelist</t>
+  </si>
+  <si>
+    <t>header(void*) - 8byte</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,29 +247,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
+      <name val="KoPubWorld돋움체 Bold"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="KoPubWorld돋움체 Bold"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="KoPubWorld돋움체 Bold"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="4"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="KoPubWorld돋움체 Bold"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -298,7 +310,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -332,56 +344,82 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -698,440 +736,469 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE06D03-E65E-4121-BF89-D913E6F20D39}">
-  <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr defaultRowHeight="23.25"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="19.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="C2" s="10" t="s">
+    <row r="1" spans="1:17" s="1" customFormat="1">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+    </row>
+    <row r="2" spans="1:17" s="1" customFormat="1">
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:17" s="1" customFormat="1">
+      <c r="C3" s="4">
+        <v>-12</v>
+      </c>
+      <c r="D3" s="4">
+        <v>-11</v>
+      </c>
+      <c r="E3" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F3" s="4">
+        <v>-9</v>
+      </c>
+      <c r="G3" s="4">
+        <v>-8</v>
+      </c>
+      <c r="H3" s="5">
+        <v>-7</v>
+      </c>
+      <c r="I3" s="5">
+        <v>-6</v>
+      </c>
+      <c r="J3" s="5">
+        <v>-5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>-4</v>
+      </c>
+      <c r="L3" s="5">
+        <v>-3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>-2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>-1</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="1" customFormat="1">
+      <c r="C4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="8"/>
+      <c r="Q4" s="9"/>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="1" customFormat="1">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="C3" s="5">
-        <v>-10</v>
-      </c>
-      <c r="D3" s="5">
-        <v>-9</v>
-      </c>
-      <c r="E3" s="5">
-        <v>-8</v>
-      </c>
-      <c r="F3" s="6">
-        <v>-7</v>
-      </c>
-      <c r="G3" s="6">
-        <v>-6</v>
-      </c>
-      <c r="H3" s="6">
-        <v>-5</v>
-      </c>
-      <c r="I3" s="6">
-        <v>-4</v>
-      </c>
-      <c r="J3" s="6">
-        <v>-3</v>
-      </c>
-      <c r="K3" s="6">
-        <v>-2</v>
-      </c>
-      <c r="L3" s="6">
-        <v>-1</v>
-      </c>
-      <c r="M3" s="6">
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="1" customFormat="1">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="7">
-        <v>1</v>
-      </c>
-      <c r="O3" s="7">
+    </row>
+    <row r="9" spans="1:17" s="1" customFormat="1">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="8"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="10" spans="1:17" s="1" customFormat="1">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="9" t="s">
+      <c r="J10" s="10"/>
+      <c r="K10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
+      <c r="L10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M10" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="3" t="s">
+    <row r="11" spans="1:17" s="1" customFormat="1">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="9" t="s">
+      <c r="J11" s="10"/>
+      <c r="K11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="3" t="s">
+      <c r="L11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="N11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="14" t="s">
+      <c r="E12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="1" customFormat="1">
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="K14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="3" t="s">
+      <c r="M14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="N14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="11" t="s">
+      <c r="O14" s="9" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="C2:M2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520E84C9-2400-4FC6-B6F2-D23AA903792C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857D8DF4-C896-4F4D-AB44-CACE6014DE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="5745" windowWidth="32055" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="1770" yWindow="6960" windowWidth="32055" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="51">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -370,57 +370,54 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -750,222 +747,235 @@
     <col min="10" max="10" width="16.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="19.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="16.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.85546875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="23.42578125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" spans="1:17" s="1" customFormat="1">
-      <c r="C2" s="2" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="C2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
-      <c r="C3" s="4">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="C3" s="2">
         <v>-12</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>-11</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>-10</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>-9</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>-8</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="3">
         <v>-7</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="3">
         <v>-6</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="3">
         <v>-5</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="3">
         <v>-4</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="3">
         <v>-3</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="3">
         <v>-2</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="3">
         <v>-1</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="3">
         <v>0</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="4">
         <v>1</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
-      <c r="C4" s="7" t="s">
+    <row r="4" spans="1:17">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
-      <c r="Q4" s="9"/>
-    </row>
-    <row r="5" spans="1:17" s="1" customFormat="1">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="6"/>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="11" t="s">
+      <c r="G5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10" t="s">
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="1" customFormat="1">
+    <row r="6" spans="1:17">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="11" t="s">
+      <c r="G6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10" t="s">
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="1" customFormat="1">
+    <row r="7" spans="1:17">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>23</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10" t="s">
+      <c r="N7" s="8"/>
+      <c r="O7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1">
+    <row r="8" spans="1:17">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -974,225 +984,243 @@
       <c r="I8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10" t="s">
+      <c r="N8" s="8"/>
+      <c r="O8" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1">
+    <row r="9" spans="1:17">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="10" t="s">
+      <c r="G9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="1" customFormat="1">
+    <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="11" t="s">
+      <c r="G10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1">
+    <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="11" t="s">
+      <c r="G11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1">
+    <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1">
+    <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="G13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="1" customFormat="1">
+    <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="F14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="10" t="s">
+      <c r="M14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="10" t="s">
+      <c r="N14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="9" t="s">
+      <c r="O14" s="7" t="s">
         <v>39</v>
       </c>
     </row>

--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857D8DF4-C896-4F4D-AB44-CACE6014DE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C478E22A-26B6-4A7F-B771-13CD019CD588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1770" yWindow="6960" windowWidth="32055" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>header(void*) - 8byte</t>
+  </si>
+  <si>
+    <t>OpenCSTL</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -386,30 +389,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -418,6 +400,42 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -753,32 +771,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
     </row>
     <row r="3" spans="1:17">
       <c r="C3" s="2">
@@ -828,23 +852,26 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="6"/>
-      <c r="Q4" s="7"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="12"/>
+      <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
@@ -853,30 +880,33 @@
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="9"/>
+      <c r="G5" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8" t="s">
+      <c r="L5" s="13"/>
+      <c r="M5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -887,30 +917,33 @@
       <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="9"/>
+      <c r="G6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9" t="s">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8" t="s">
+      <c r="L6" s="13"/>
+      <c r="M6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -921,38 +954,39 @@
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8" t="s">
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="s">
         <v>16</v>
       </c>
     </row>
@@ -963,41 +997,41 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8" t="s">
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1008,30 +1042,33 @@
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="9"/>
+      <c r="G9" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="8" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1042,32 +1079,35 @@
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="9"/>
+      <c r="G10" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="9" t="s">
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1078,32 +1118,35 @@
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="9"/>
+      <c r="G11" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9" t="s">
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1114,28 +1157,33 @@
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="13" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1143,40 +1191,41 @@
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="9"/>
+      <c r="G13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="M13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="O13" s="14" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1184,49 +1233,50 @@
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="M14" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="7" t="s">
+      <c r="O14" s="14" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C2:M2"/>
+    <mergeCell ref="B1:O1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C478E22A-26B6-4A7F-B771-13CD019CD588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8460E606-E663-43E7-A0AF-0039D13D13C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="6960" windowWidth="32055" windowHeight="17190" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="1605" yWindow="435" windowWidth="32055" windowHeight="10365" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -199,9 +199,6 @@
     <t>hash func</t>
   </si>
   <si>
-    <t>bloom filter</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -227,6 +224,12 @@
   </si>
   <si>
     <t>OpenCSTL</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>tombstone</t>
   </si>
 </sst>
 </file>
@@ -395,16 +398,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -436,6 +430,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,7 +763,7 @@
     <col min="4" max="4" width="19.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" style="1" customWidth="1"/>
     <col min="6" max="7" width="19.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="39.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.42578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="19.42578125" style="1" customWidth="1"/>
@@ -772,37 +775,37 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="6"/>
-      <c r="B1" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
+      <c r="B1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="C2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
+      <c r="C2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:17">
       <c r="C3" s="2">
@@ -852,25 +855,25 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="12"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="9"/>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17">
@@ -880,33 +883,33 @@
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="15" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13" t="s">
+      <c r="L5" s="10"/>
+      <c r="M5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O5" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -917,33 +920,33 @@
       <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="15" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13" t="s">
+      <c r="L6" s="10"/>
+      <c r="M6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -954,39 +957,39 @@
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M7" s="17" t="s">
+      <c r="J7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13" t="s">
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -997,41 +1000,41 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="s">
+      <c r="N8" s="10"/>
+      <c r="O8" s="10" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1042,33 +1045,33 @@
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="13" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1079,35 +1082,35 @@
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="15" t="s">
+      <c r="F10" s="7"/>
+      <c r="G10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="13" t="s">
+      <c r="N10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="13" t="s">
+      <c r="O10" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1118,35 +1121,35 @@
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="15" t="s">
+      <c r="F11" s="7"/>
+      <c r="G11" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="N11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="O11" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1157,33 +1160,33 @@
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="15" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="13" t="s">
+      <c r="O12" s="10" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1191,41 +1194,41 @@
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="17" t="s">
+      <c r="E13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O13" s="14" t="s">
+      <c r="O13" s="11" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1233,43 +1236,43 @@
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="14" t="s">
+      <c r="E14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="G14" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="13" t="s">
+      <c r="N14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="14" t="s">
+      <c r="O14" s="11" t="s">
         <v>39</v>
       </c>
     </row>

--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8460E606-E663-43E7-A0AF-0039D13D13C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45AEF4C-E3CC-4956-A9FE-49396456D532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1605" yWindow="435" windowWidth="32055" windowHeight="10365" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="3135" yWindow="495" windowWidth="32055" windowHeight="12990" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -220,9 +220,6 @@
     <t>freelist</t>
   </si>
   <si>
-    <t>header(void*) - 8byte</t>
-  </si>
-  <si>
     <t>OpenCSTL</t>
   </si>
   <si>
@@ -230,13 +227,16 @@
   </si>
   <si>
     <t>tombstone</t>
+  </si>
+  <si>
+    <t>header(void*) - 96 (12x8)byte</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +277,19 @@
       <name val="KoPubWorld돋움체 Bold"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="KoPubWorld돋움체 Bold"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="KoPubWorld돋움체 Bold"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -284,12 +297,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -312,6 +319,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC4436"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,68 +389,65 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,6 +456,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFDC4436"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -773,28 +788,27 @@
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="6"/>
-      <c r="B1" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+    <row r="1" spans="1:17" ht="32.25">
+      <c r="B1" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" ht="25.5">
       <c r="C2" s="18" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="19"/>
@@ -855,25 +869,25 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="9"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="8"/>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17">
@@ -883,33 +897,33 @@
       <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="11" t="s">
+      <c r="F5" s="6"/>
+      <c r="G5" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="12" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10" t="s">
+      <c r="L5" s="9"/>
+      <c r="M5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -920,33 +934,33 @@
       <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="12" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10" t="s">
+      <c r="L6" s="9"/>
+      <c r="M6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -957,39 +971,39 @@
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="11" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10" t="s">
+      <c r="N7" s="9"/>
+      <c r="O7" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1000,41 +1014,41 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10" t="s">
+      <c r="N8" s="9"/>
+      <c r="O8" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1045,33 +1059,33 @@
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="11" t="s">
+      <c r="F9" s="6"/>
+      <c r="G9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="10" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1082,35 +1096,35 @@
       <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="11" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="12" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1121,35 +1135,35 @@
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="11" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="12" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1160,33 +1174,33 @@
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="12" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1194,41 +1208,41 @@
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="11" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="M13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1236,43 +1250,43 @@
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="10" t="s">
+      <c r="I14" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="14" t="s">
+      <c r="M14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="N14" s="10" t="s">
+      <c r="N14" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="10" t="s">
         <v>39</v>
       </c>
     </row>

--- a/test/OpenCSTL.xlsx
+++ b/test/OpenCSTL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45AEF4C-E3CC-4956-A9FE-49396456D532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9382198-8143-4EB8-B420-47C3DB1FC3E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="495" windowWidth="32055" windowHeight="12990" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="1395" yWindow="2835" windowWidth="32055" windowHeight="15030" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,16 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="59">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_vector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>base</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -86,10 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPENCSTL_LIST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -106,26 +98,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_set</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPENCSTL_SET</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_map</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPENCSTL_MAP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_deque</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPENCSTL_DEQUE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -142,22 +122,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>type*</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type**</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>opencstl_stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>opencstl_queue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPENCSTL_STACK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,10 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_priority_queue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OPENCSTL_PRIORITY_QUEUE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,12 +138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>opencstl_unordered_map</t>
-  </si>
-  <si>
-    <t>opencstl_unordered_set</t>
-  </si>
-  <si>
     <t>OPENCSTL_UNORDERED_SET</t>
   </si>
   <si>
@@ -229,14 +183,68 @@
     <t>tombstone</t>
   </si>
   <si>
-    <t>header(void*) - 96 (12x8)byte</t>
+    <t>OPENCSTL_ARRAY</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>TYPE*</t>
+  </si>
+  <si>
+    <t>TYPE**</t>
+  </si>
+  <si>
+    <t>ARRAY</t>
+  </si>
+  <si>
+    <t>VECTOR</t>
+  </si>
+  <si>
+    <t>LIST</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>MAP</t>
+  </si>
+  <si>
+    <t>DEQUE</t>
+  </si>
+  <si>
+    <t>STACK</t>
+  </si>
+  <si>
+    <t>QUEUE</t>
+  </si>
+  <si>
+    <t>PRIORITY_QUEUE</t>
+  </si>
+  <si>
+    <t>UNORDERED_SET</t>
+  </si>
+  <si>
+    <t>UNORDERED_MAP</t>
+  </si>
+  <si>
+    <t>header(void*) - 96 (12x8) byte</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>[2]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,34 +268,65 @@
     </font>
     <font>
       <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="KoPubWorld돋움체 Bold"/>
+      <name val="나눔스퀘어 Bold"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="나눔스퀘어 Bold"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
-      <name val="KoPubWorld돋움체 Bold"/>
+      <name val="나눔스퀘어 Bold"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="4"/>
-      <name val="KoPubWorld돋움체 Bold"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="0"/>
-      <name val="KoPubWorld돋움체 Bold"/>
+      <name val="나눔스퀘어 Bold"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="KoPubWorld돋움체 Bold"/>
+      <name val="나눔스퀘어 ExtraBold"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="나눔스퀘어 Bold"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -297,18 +336,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -324,12 +351,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC4436"/>
+        <fgColor rgb="FF253E82"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6F9EF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1DAFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -356,31 +395,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -389,65 +406,59 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -458,6 +469,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF253E82"/>
+      <color rgb="FFD1DAFF"/>
+      <color rgb="FFF9F5FE"/>
+      <color rgb="FF6F9EF7"/>
       <color rgb="FFDC4436"/>
     </mruColors>
   </colors>
@@ -769,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE06D03-E65E-4121-BF89-D913E6F20D39}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="23.25"/>
   <cols>
     <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
@@ -788,77 +803,87 @@
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="32.25">
-      <c r="B1" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
+    <row r="1" spans="1:17" ht="31.5">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:17" ht="25.5">
-      <c r="C2" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
+    <row r="2" spans="1:17" ht="24.75">
+      <c r="A2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
     </row>
     <row r="3" spans="1:17">
-      <c r="C3" s="2">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4">
         <v>-12</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>-11</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="4">
         <v>-10</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>-9</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="4">
         <v>-8</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="4">
         <v>-7</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="4">
         <v>-6</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="4">
         <v>-5</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="4">
         <v>-4</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="4">
         <v>-3</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="4">
         <v>-2</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="4">
         <v>-1</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="4">
         <v>0</v>
       </c>
       <c r="P3" s="4">
@@ -869,431 +894,545 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="8"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="12"/>
+      <c r="G5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>2</v>
+      <c r="P5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" s="9" t="s">
+      <c r="A6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>14</v>
+      <c r="N6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="A7" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="9" t="s">
+      <c r="B7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9" t="s">
-        <v>16</v>
+      <c r="C7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="6" t="s">
+      <c r="A8" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="9" t="s">
+      <c r="B8" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9" t="s">
-        <v>0</v>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="9" t="s">
-        <v>4</v>
+      <c r="A9" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="9" t="s">
+      <c r="A10" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>2</v>
+      <c r="O10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="9" t="s">
+      <c r="A11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="G11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>2</v>
+      <c r="O11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="9" t="s">
+      <c r="K12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>2</v>
+      <c r="O12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="A13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" s="9" t="s">
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O13" s="10" t="s">
-        <v>39</v>
+      <c r="N13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="9" t="s">
+      <c r="I14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" s="9" t="s">
+      <c r="C15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="I15" s="13" t="s">
         <v>39</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C2:M2"/>
-    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="C2:N2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
